--- a/test_instances/T2_small_2containers.xlsx
+++ b/test_instances/T2_small_2containers.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Pallet size</t>
+          <t>Pallet type</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -446,7 +446,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>External Packaging Quantity</t>
+          <t>Order External Packaging Quantity</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
